--- a/배차작업/배차원근무조편성/본사_배차원_48주.xlsx
+++ b/배차작업/배차원근무조편성/본사_배차원_48주.xlsx
@@ -1,17 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="870" windowWidth="33120" windowHeight="12045" activeTab="1"/>
+    <workbookView xWindow="816" yWindow="876" windowWidth="33120" windowHeight="12048" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="근무표 인쇄용" sheetId="2" r:id="rId1"/>
     <sheet name="48주 로테이션 근무표" sheetId="1" r:id="rId2"/>
+    <sheet name="48주 로테이션 근무표 간략본" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'48주 로테이션 근무표'!$A:$AE</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'48주 로테이션 근무표 간략본'!$A:$AD</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'근무표 인쇄용'!$A$1:$AE$88</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
@@ -19,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4646" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5398" uniqueCount="110">
   <si>
     <t>※ 주간 전담 순서: 1. 차현철 → 2. 진영만 → 3. 박원호 → 4. 한원석 (12주 단위 / 한 줄에 4주씩 배치)</t>
   </si>
@@ -351,12 +353,52 @@
     <t>월</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>23주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>24주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>35주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>36주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>47주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>48주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>59주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>60주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>49주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>50주</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="15" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -469,7 +511,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -542,6 +584,12 @@
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -607,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -670,14 +718,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -687,6 +736,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -985,92 +1038,92 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B2:AT88"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="1.375" style="22" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="22" customWidth="1"/>
+    <col min="1" max="1" width="1.3984375" style="22" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" style="22" customWidth="1"/>
     <col min="3" max="30" width="7" style="22" customWidth="1"/>
-    <col min="31" max="31" width="1.125" style="22" customWidth="1"/>
-    <col min="32" max="16384" width="8.75" style="22"/>
+    <col min="31" max="31" width="1.09765625" style="22" customWidth="1"/>
+    <col min="32" max="16384" width="8.69921875" style="22"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B2" s="28" t="s">
+    <row r="2" spans="2:46">
+      <c r="B2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-    </row>
-    <row r="3" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+    </row>
+    <row r="3" spans="2:46">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="30" t="s">
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="30" t="s">
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="30" t="s">
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="Y3" s="31"/>
-      <c r="Z3" s="31"/>
-      <c r="AA3" s="31"/>
-      <c r="AB3" s="31"/>
-      <c r="AC3" s="31"/>
-      <c r="AD3" s="31"/>
-    </row>
-    <row r="4" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="30"/>
+    </row>
+    <row r="4" spans="2:46">
       <c r="B4" s="1"/>
       <c r="C4" s="2" t="s">
         <v>75</v>
@@ -1157,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:46">
       <c r="B5" s="1" t="s">
         <v>67</v>
       </c>
@@ -1246,7 +1299,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:46">
       <c r="B6" s="1" t="s">
         <v>68</v>
       </c>
@@ -1335,7 +1388,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:46">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -1424,7 +1477,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:46">
       <c r="B8" s="1" t="s">
         <v>70</v>
       </c>
@@ -1513,7 +1566,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:46" hidden="1">
       <c r="AN9" s="20" t="s">
         <v>96</v>
       </c>
@@ -1521,55 +1574,55 @@
       <c r="AP9" s="20"/>
       <c r="AQ9" s="20"/>
     </row>
-    <row r="10" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:46" hidden="1">
       <c r="B10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="32" t="s">
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="32" t="s">
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="34"/>
-      <c r="X10" s="32" t="s">
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="34"/>
+      <c r="V10" s="34"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="33"/>
-      <c r="AA10" s="33"/>
-      <c r="AB10" s="33"/>
-      <c r="AC10" s="33"/>
-      <c r="AD10" s="34"/>
-      <c r="AF10" s="32" t="s">
+      <c r="Y10" s="34"/>
+      <c r="Z10" s="34"/>
+      <c r="AA10" s="34"/>
+      <c r="AB10" s="34"/>
+      <c r="AC10" s="34"/>
+      <c r="AD10" s="35"/>
+      <c r="AF10" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="AG10" s="33"/>
-      <c r="AH10" s="33"/>
-      <c r="AI10" s="33"/>
-      <c r="AJ10" s="33"/>
-      <c r="AK10" s="33"/>
-      <c r="AL10" s="34"/>
+      <c r="AG10" s="34"/>
+      <c r="AH10" s="34"/>
+      <c r="AI10" s="34"/>
+      <c r="AJ10" s="34"/>
+      <c r="AK10" s="34"/>
+      <c r="AL10" s="35"/>
       <c r="AN10" s="21" t="s">
         <v>90</v>
       </c>
@@ -1577,7 +1630,7 @@
       <c r="AP10" s="21"/>
       <c r="AQ10" s="21"/>
     </row>
-    <row r="11" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:46" hidden="1">
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
         <v>78</v>
@@ -1706,7 +1759,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:46">
       <c r="B12" s="1" t="s">
         <v>67</v>
       </c>
@@ -1841,7 +1894,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:46">
       <c r="B13" s="1" t="s">
         <v>68</v>
       </c>
@@ -1976,7 +2029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:46">
       <c r="B14" s="1" t="s">
         <v>69</v>
       </c>
@@ -2111,7 +2164,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:46">
       <c r="B15" s="1" t="s">
         <v>70</v>
       </c>
@@ -2246,56 +2299,56 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:46" hidden="1"/>
+    <row r="17" spans="2:46" hidden="1">
       <c r="B17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="32" t="s">
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="32" t="s">
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="33"/>
-      <c r="V17" s="33"/>
-      <c r="W17" s="34"/>
-      <c r="X17" s="32" t="s">
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="34"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="Y17" s="33"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="33"/>
-      <c r="AB17" s="33"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="34"/>
-      <c r="AF17" s="32" t="s">
+      <c r="Y17" s="34"/>
+      <c r="Z17" s="34"/>
+      <c r="AA17" s="34"/>
+      <c r="AB17" s="34"/>
+      <c r="AC17" s="34"/>
+      <c r="AD17" s="35"/>
+      <c r="AF17" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="AG17" s="33"/>
-      <c r="AH17" s="33"/>
-      <c r="AI17" s="33"/>
-      <c r="AJ17" s="33"/>
-      <c r="AK17" s="33"/>
-      <c r="AL17" s="34"/>
+      <c r="AG17" s="34"/>
+      <c r="AH17" s="34"/>
+      <c r="AI17" s="34"/>
+      <c r="AJ17" s="34"/>
+      <c r="AK17" s="34"/>
+      <c r="AL17" s="35"/>
       <c r="AN17" s="21" t="s">
         <v>91</v>
       </c>
@@ -2303,7 +2356,7 @@
       <c r="AP17" s="21"/>
       <c r="AQ17" s="21"/>
     </row>
-    <row r="18" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:46" hidden="1">
       <c r="B18" s="1"/>
       <c r="C18" s="2" t="s">
         <v>79</v>
@@ -2432,7 +2485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:46">
       <c r="B19" s="1" t="s">
         <v>67</v>
       </c>
@@ -2567,7 +2620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:46">
       <c r="B20" s="1" t="s">
         <v>68</v>
       </c>
@@ -2702,7 +2755,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:46">
       <c r="B21" s="1" t="s">
         <v>69</v>
       </c>
@@ -2837,7 +2890,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:46">
       <c r="B22" s="1" t="s">
         <v>70</v>
       </c>
@@ -2972,39 +3025,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B24" s="28" t="s">
+    <row r="23" spans="2:46" hidden="1"/>
+    <row r="24" spans="2:46">
+      <c r="B24" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-      <c r="W24" s="29"/>
-      <c r="X24" s="29"/>
-      <c r="Y24" s="29"/>
-      <c r="Z24" s="29"/>
-      <c r="AA24" s="29"/>
-      <c r="AB24" s="29"/>
-      <c r="AC24" s="29"/>
-      <c r="AD24" s="29"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="32"/>
+      <c r="AA24" s="32"/>
+      <c r="AB24" s="32"/>
+      <c r="AC24" s="32"/>
+      <c r="AD24" s="32"/>
       <c r="AN24" s="20" t="s">
         <v>95</v>
       </c>
@@ -3012,55 +3065,55 @@
       <c r="AP24" s="20"/>
       <c r="AQ24" s="20"/>
     </row>
-    <row r="25" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:46">
       <c r="B25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="30" t="s">
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="30" t="s">
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="30" t="s">
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="Y25" s="31"/>
-      <c r="Z25" s="31"/>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
-      <c r="AF25" s="30" t="s">
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="30"/>
+      <c r="AA25" s="30"/>
+      <c r="AB25" s="30"/>
+      <c r="AC25" s="30"/>
+      <c r="AD25" s="30"/>
+      <c r="AF25" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="AG25" s="31"/>
-      <c r="AH25" s="31"/>
-      <c r="AI25" s="31"/>
-      <c r="AJ25" s="31"/>
-      <c r="AK25" s="31"/>
-      <c r="AL25" s="31"/>
+      <c r="AG25" s="30"/>
+      <c r="AH25" s="30"/>
+      <c r="AI25" s="30"/>
+      <c r="AJ25" s="30"/>
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="30"/>
       <c r="AN25" s="21" t="s">
         <v>90</v>
       </c>
@@ -3068,7 +3121,7 @@
       <c r="AP25" s="21"/>
       <c r="AQ25" s="21"/>
     </row>
-    <row r="26" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:46">
       <c r="B26" s="1"/>
       <c r="C26" s="14" t="s">
         <v>80</v>
@@ -3197,7 +3250,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:46">
       <c r="B27" s="1" t="s">
         <v>67</v>
       </c>
@@ -3331,7 +3384,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:46">
       <c r="B28" s="1" t="s">
         <v>68</v>
       </c>
@@ -3465,7 +3518,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:46">
       <c r="B29" s="1" t="s">
         <v>69</v>
       </c>
@@ -3599,7 +3652,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:46">
       <c r="B30" s="1" t="s">
         <v>70</v>
       </c>
@@ -3733,56 +3786,56 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:46" hidden="1"/>
+    <row r="32" spans="2:46" hidden="1">
       <c r="B32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="32" t="s">
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="32" t="s">
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="R32" s="33"/>
-      <c r="S32" s="33"/>
-      <c r="T32" s="33"/>
-      <c r="U32" s="33"/>
-      <c r="V32" s="33"/>
-      <c r="W32" s="34"/>
-      <c r="X32" s="32" t="s">
+      <c r="R32" s="34"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="34"/>
+      <c r="V32" s="34"/>
+      <c r="W32" s="35"/>
+      <c r="X32" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="Y32" s="33"/>
-      <c r="Z32" s="33"/>
-      <c r="AA32" s="33"/>
-      <c r="AB32" s="33"/>
-      <c r="AC32" s="33"/>
-      <c r="AD32" s="34"/>
-      <c r="AF32" s="32" t="s">
+      <c r="Y32" s="34"/>
+      <c r="Z32" s="34"/>
+      <c r="AA32" s="34"/>
+      <c r="AB32" s="34"/>
+      <c r="AC32" s="34"/>
+      <c r="AD32" s="35"/>
+      <c r="AF32" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="AG32" s="33"/>
-      <c r="AH32" s="33"/>
-      <c r="AI32" s="33"/>
-      <c r="AJ32" s="33"/>
-      <c r="AK32" s="33"/>
-      <c r="AL32" s="34"/>
+      <c r="AG32" s="34"/>
+      <c r="AH32" s="34"/>
+      <c r="AI32" s="34"/>
+      <c r="AJ32" s="34"/>
+      <c r="AK32" s="34"/>
+      <c r="AL32" s="35"/>
       <c r="AN32" s="21" t="s">
         <v>91</v>
       </c>
@@ -3790,7 +3843,7 @@
       <c r="AP32" s="21"/>
       <c r="AQ32" s="21"/>
     </row>
-    <row r="33" spans="2:46" s="17" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:46" s="17" customFormat="1" hidden="1">
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="s">
         <v>81</v>
@@ -3920,7 +3973,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:46">
       <c r="B34" s="1" t="s">
         <v>67</v>
       </c>
@@ -4054,7 +4107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:46">
       <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
@@ -4188,7 +4241,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:46">
       <c r="B36" s="1" t="s">
         <v>69</v>
       </c>
@@ -4322,7 +4375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:46">
       <c r="B37" s="1" t="s">
         <v>70</v>
       </c>
@@ -4456,49 +4509,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:46" hidden="1"/>
+    <row r="39" spans="2:46" hidden="1">
       <c r="B39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="32" t="s">
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="33"/>
-      <c r="O39" s="33"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="32" t="s">
+      <c r="K39" s="34"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="34"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="34"/>
+      <c r="P39" s="35"/>
+      <c r="Q39" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="R39" s="33"/>
-      <c r="S39" s="33"/>
-      <c r="T39" s="33"/>
-      <c r="U39" s="33"/>
-      <c r="V39" s="33"/>
-      <c r="W39" s="34"/>
-      <c r="X39" s="32" t="s">
+      <c r="R39" s="34"/>
+      <c r="S39" s="34"/>
+      <c r="T39" s="34"/>
+      <c r="U39" s="34"/>
+      <c r="V39" s="34"/>
+      <c r="W39" s="35"/>
+      <c r="X39" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="Y39" s="33"/>
-      <c r="Z39" s="33"/>
-      <c r="AA39" s="33"/>
-      <c r="AB39" s="33"/>
-      <c r="AC39" s="33"/>
-      <c r="AD39" s="34"/>
-    </row>
-    <row r="40" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y39" s="34"/>
+      <c r="Z39" s="34"/>
+      <c r="AA39" s="34"/>
+      <c r="AB39" s="34"/>
+      <c r="AC39" s="34"/>
+      <c r="AD39" s="35"/>
+    </row>
+    <row r="40" spans="2:46" hidden="1">
       <c r="B40" s="1"/>
       <c r="C40" s="14" t="s">
         <v>82</v>
@@ -4585,7 +4638,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:46">
       <c r="B41" s="1" t="s">
         <v>67</v>
       </c>
@@ -4674,7 +4727,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:46">
       <c r="B42" s="1" t="s">
         <v>68</v>
       </c>
@@ -4763,7 +4816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:46">
       <c r="B43" s="1" t="s">
         <v>69</v>
       </c>
@@ -4852,7 +4905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:46">
       <c r="B44" s="1" t="s">
         <v>70</v>
       </c>
@@ -4941,82 +4994,82 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B46" s="28" t="s">
+    <row r="45" spans="2:46" hidden="1"/>
+    <row r="46" spans="2:46">
+      <c r="B46" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
-      <c r="AA46" s="29"/>
-      <c r="AB46" s="29"/>
-      <c r="AC46" s="29"/>
-      <c r="AD46" s="29"/>
-    </row>
-    <row r="47" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="32"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
+      <c r="V46" s="32"/>
+      <c r="W46" s="32"/>
+      <c r="X46" s="32"/>
+      <c r="Y46" s="32"/>
+      <c r="Z46" s="32"/>
+      <c r="AA46" s="32"/>
+      <c r="AB46" s="32"/>
+      <c r="AC46" s="32"/>
+      <c r="AD46" s="32"/>
+    </row>
+    <row r="47" spans="2:46">
       <c r="B47" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C47" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="30" t="s">
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="30" t="s">
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="31"/>
-      <c r="U47" s="31"/>
-      <c r="V47" s="31"/>
-      <c r="W47" s="31"/>
-      <c r="X47" s="30" t="s">
+      <c r="R47" s="30"/>
+      <c r="S47" s="30"/>
+      <c r="T47" s="30"/>
+      <c r="U47" s="30"/>
+      <c r="V47" s="30"/>
+      <c r="W47" s="30"/>
+      <c r="X47" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="Y47" s="31"/>
-      <c r="Z47" s="31"/>
-      <c r="AA47" s="31"/>
-      <c r="AB47" s="31"/>
-      <c r="AC47" s="31"/>
-      <c r="AD47" s="31"/>
-    </row>
-    <row r="48" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="Y47" s="30"/>
+      <c r="Z47" s="30"/>
+      <c r="AA47" s="30"/>
+      <c r="AB47" s="30"/>
+      <c r="AC47" s="30"/>
+      <c r="AD47" s="30"/>
+    </row>
+    <row r="48" spans="2:46">
       <c r="B48" s="1"/>
       <c r="C48" s="2" t="s">
         <v>83</v>
@@ -5103,7 +5156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:30">
       <c r="B49" s="1" t="s">
         <v>67</v>
       </c>
@@ -5192,7 +5245,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:30">
       <c r="B50" s="1" t="s">
         <v>68</v>
       </c>
@@ -5281,7 +5334,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:30">
       <c r="B51" s="1" t="s">
         <v>69</v>
       </c>
@@ -5370,7 +5423,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:30">
       <c r="B52" s="1" t="s">
         <v>70</v>
       </c>
@@ -5459,49 +5512,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="2:30" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:30" hidden="1"/>
+    <row r="54" spans="2:30" hidden="1">
       <c r="B54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="30" t="s">
+      <c r="C54" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="30" t="s">
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="K54" s="31"/>
-      <c r="L54" s="31"/>
-      <c r="M54" s="31"/>
-      <c r="N54" s="31"/>
-      <c r="O54" s="31"/>
-      <c r="P54" s="31"/>
-      <c r="Q54" s="30" t="s">
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+      <c r="Q54" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="R54" s="31"/>
-      <c r="S54" s="31"/>
-      <c r="T54" s="31"/>
-      <c r="U54" s="31"/>
-      <c r="V54" s="31"/>
-      <c r="W54" s="31"/>
-      <c r="X54" s="30" t="s">
+      <c r="R54" s="30"/>
+      <c r="S54" s="30"/>
+      <c r="T54" s="30"/>
+      <c r="U54" s="30"/>
+      <c r="V54" s="30"/>
+      <c r="W54" s="30"/>
+      <c r="X54" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="Y54" s="31"/>
-      <c r="Z54" s="31"/>
-      <c r="AA54" s="31"/>
-      <c r="AB54" s="31"/>
-      <c r="AC54" s="31"/>
-      <c r="AD54" s="31"/>
-    </row>
-    <row r="55" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y54" s="30"/>
+      <c r="Z54" s="30"/>
+      <c r="AA54" s="30"/>
+      <c r="AB54" s="30"/>
+      <c r="AC54" s="30"/>
+      <c r="AD54" s="30"/>
+    </row>
+    <row r="55" spans="2:30" hidden="1">
       <c r="B55" s="1"/>
       <c r="C55" s="2" t="s">
         <v>84</v>
@@ -5588,7 +5641,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:30">
       <c r="B56" s="1" t="s">
         <v>67</v>
       </c>
@@ -5677,7 +5730,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:30">
       <c r="B57" s="1" t="s">
         <v>68</v>
       </c>
@@ -5766,7 +5819,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:30">
       <c r="B58" s="1" t="s">
         <v>69</v>
       </c>
@@ -5855,7 +5908,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:30">
       <c r="B59" s="1" t="s">
         <v>70</v>
       </c>
@@ -5944,49 +5997,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="2:30" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:30" hidden="1"/>
+    <row r="61" spans="2:30" hidden="1">
       <c r="B61" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C61" s="30" t="s">
+      <c r="C61" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="30" t="s">
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
-      <c r="N61" s="31"/>
-      <c r="O61" s="31"/>
-      <c r="P61" s="31"/>
-      <c r="Q61" s="30" t="s">
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="R61" s="31"/>
-      <c r="S61" s="31"/>
-      <c r="T61" s="31"/>
-      <c r="U61" s="31"/>
-      <c r="V61" s="31"/>
-      <c r="W61" s="31"/>
-      <c r="X61" s="30" t="s">
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="Y61" s="31"/>
-      <c r="Z61" s="31"/>
-      <c r="AA61" s="31"/>
-      <c r="AB61" s="31"/>
-      <c r="AC61" s="31"/>
-      <c r="AD61" s="31"/>
-    </row>
-    <row r="62" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30"/>
+      <c r="AC61" s="30"/>
+      <c r="AD61" s="30"/>
+    </row>
+    <row r="62" spans="2:30" hidden="1">
       <c r="B62" s="1"/>
       <c r="C62" s="2" t="s">
         <v>86</v>
@@ -6073,7 +6126,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:30">
       <c r="B63" s="1" t="s">
         <v>67</v>
       </c>
@@ -6162,7 +6215,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:30">
       <c r="B64" s="1" t="s">
         <v>68</v>
       </c>
@@ -6251,7 +6304,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:30">
       <c r="B65" s="1" t="s">
         <v>69</v>
       </c>
@@ -6340,7 +6393,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:30">
       <c r="B66" s="1" t="s">
         <v>70</v>
       </c>
@@ -6429,82 +6482,82 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="2:30" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B68" s="28" t="s">
+    <row r="67" spans="2:30" hidden="1"/>
+    <row r="68" spans="2:30">
+      <c r="B68" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="29"/>
-      <c r="I68" s="29"/>
-      <c r="J68" s="29"/>
-      <c r="K68" s="29"/>
-      <c r="L68" s="29"/>
-      <c r="M68" s="29"/>
-      <c r="N68" s="29"/>
-      <c r="O68" s="29"/>
-      <c r="P68" s="29"/>
-      <c r="Q68" s="29"/>
-      <c r="R68" s="29"/>
-      <c r="S68" s="29"/>
-      <c r="T68" s="29"/>
-      <c r="U68" s="29"/>
-      <c r="V68" s="29"/>
-      <c r="W68" s="29"/>
-      <c r="X68" s="29"/>
-      <c r="Y68" s="29"/>
-      <c r="Z68" s="29"/>
-      <c r="AA68" s="29"/>
-      <c r="AB68" s="29"/>
-      <c r="AC68" s="29"/>
-      <c r="AD68" s="29"/>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="32"/>
+      <c r="L68" s="32"/>
+      <c r="M68" s="32"/>
+      <c r="N68" s="32"/>
+      <c r="O68" s="32"/>
+      <c r="P68" s="32"/>
+      <c r="Q68" s="32"/>
+      <c r="R68" s="32"/>
+      <c r="S68" s="32"/>
+      <c r="T68" s="32"/>
+      <c r="U68" s="32"/>
+      <c r="V68" s="32"/>
+      <c r="W68" s="32"/>
+      <c r="X68" s="32"/>
+      <c r="Y68" s="32"/>
+      <c r="Z68" s="32"/>
+      <c r="AA68" s="32"/>
+      <c r="AB68" s="32"/>
+      <c r="AC68" s="32"/>
+      <c r="AD68" s="32"/>
+    </row>
+    <row r="69" spans="2:30">
       <c r="B69" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="30" t="s">
+      <c r="C69" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="31"/>
-      <c r="J69" s="30" t="s">
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="K69" s="31"/>
-      <c r="L69" s="31"/>
-      <c r="M69" s="31"/>
-      <c r="N69" s="31"/>
-      <c r="O69" s="31"/>
-      <c r="P69" s="31"/>
-      <c r="Q69" s="30" t="s">
+      <c r="K69" s="30"/>
+      <c r="L69" s="30"/>
+      <c r="M69" s="30"/>
+      <c r="N69" s="30"/>
+      <c r="O69" s="30"/>
+      <c r="P69" s="30"/>
+      <c r="Q69" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R69" s="31"/>
-      <c r="S69" s="31"/>
-      <c r="T69" s="31"/>
-      <c r="U69" s="31"/>
-      <c r="V69" s="31"/>
-      <c r="W69" s="31"/>
-      <c r="X69" s="30" t="s">
+      <c r="R69" s="30"/>
+      <c r="S69" s="30"/>
+      <c r="T69" s="30"/>
+      <c r="U69" s="30"/>
+      <c r="V69" s="30"/>
+      <c r="W69" s="30"/>
+      <c r="X69" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="Y69" s="31"/>
-      <c r="Z69" s="31"/>
-      <c r="AA69" s="31"/>
-      <c r="AB69" s="31"/>
-      <c r="AC69" s="31"/>
-      <c r="AD69" s="31"/>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y69" s="30"/>
+      <c r="Z69" s="30"/>
+      <c r="AA69" s="30"/>
+      <c r="AB69" s="30"/>
+      <c r="AC69" s="30"/>
+      <c r="AD69" s="30"/>
+    </row>
+    <row r="70" spans="2:30">
       <c r="B70" s="1"/>
       <c r="C70" s="2" t="s">
         <v>87</v>
@@ -6591,7 +6644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:30">
       <c r="B71" s="1" t="s">
         <v>67</v>
       </c>
@@ -6680,7 +6733,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:30">
       <c r="B72" s="1" t="s">
         <v>68</v>
       </c>
@@ -6769,7 +6822,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:30">
       <c r="B73" s="1" t="s">
         <v>69</v>
       </c>
@@ -6858,7 +6911,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:30">
       <c r="B74" s="1" t="s">
         <v>70</v>
       </c>
@@ -6947,49 +7000,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="2:30" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:30" hidden="1"/>
+    <row r="76" spans="2:30" hidden="1">
       <c r="B76" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C76" s="30" t="s">
+      <c r="C76" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D76" s="31"/>
-      <c r="E76" s="31"/>
-      <c r="F76" s="31"/>
-      <c r="G76" s="31"/>
-      <c r="H76" s="31"/>
-      <c r="I76" s="31"/>
-      <c r="J76" s="30" t="s">
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="K76" s="31"/>
-      <c r="L76" s="31"/>
-      <c r="M76" s="31"/>
-      <c r="N76" s="31"/>
-      <c r="O76" s="31"/>
-      <c r="P76" s="31"/>
-      <c r="Q76" s="30" t="s">
+      <c r="K76" s="30"/>
+      <c r="L76" s="30"/>
+      <c r="M76" s="30"/>
+      <c r="N76" s="30"/>
+      <c r="O76" s="30"/>
+      <c r="P76" s="30"/>
+      <c r="Q76" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="R76" s="31"/>
-      <c r="S76" s="31"/>
-      <c r="T76" s="31"/>
-      <c r="U76" s="31"/>
-      <c r="V76" s="31"/>
-      <c r="W76" s="31"/>
-      <c r="X76" s="30" t="s">
+      <c r="R76" s="30"/>
+      <c r="S76" s="30"/>
+      <c r="T76" s="30"/>
+      <c r="U76" s="30"/>
+      <c r="V76" s="30"/>
+      <c r="W76" s="30"/>
+      <c r="X76" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="Y76" s="31"/>
-      <c r="Z76" s="31"/>
-      <c r="AA76" s="31"/>
-      <c r="AB76" s="31"/>
-      <c r="AC76" s="31"/>
-      <c r="AD76" s="31"/>
-    </row>
-    <row r="77" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y76" s="30"/>
+      <c r="Z76" s="30"/>
+      <c r="AA76" s="30"/>
+      <c r="AB76" s="30"/>
+      <c r="AC76" s="30"/>
+      <c r="AD76" s="30"/>
+    </row>
+    <row r="77" spans="2:30" hidden="1">
       <c r="B77" s="1"/>
       <c r="C77" s="2" t="s">
         <v>88</v>
@@ -7076,7 +7129,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:30">
       <c r="B78" s="1" t="s">
         <v>67</v>
       </c>
@@ -7165,7 +7218,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:30">
       <c r="B79" s="1" t="s">
         <v>68</v>
       </c>
@@ -7254,7 +7307,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:30">
       <c r="B80" s="1" t="s">
         <v>69</v>
       </c>
@@ -7343,7 +7396,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:30">
       <c r="B81" s="1" t="s">
         <v>70</v>
       </c>
@@ -7432,49 +7485,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="2:30" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:30" hidden="1"/>
+    <row r="83" spans="2:30" hidden="1">
       <c r="B83" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C83" s="30" t="s">
+      <c r="C83" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D83" s="31"/>
-      <c r="E83" s="31"/>
-      <c r="F83" s="31"/>
-      <c r="G83" s="31"/>
-      <c r="H83" s="31"/>
-      <c r="I83" s="31"/>
-      <c r="J83" s="30" t="s">
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="30"/>
+      <c r="H83" s="30"/>
+      <c r="I83" s="30"/>
+      <c r="J83" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="K83" s="31"/>
-      <c r="L83" s="31"/>
-      <c r="M83" s="31"/>
-      <c r="N83" s="31"/>
-      <c r="O83" s="31"/>
-      <c r="P83" s="31"/>
-      <c r="Q83" s="30" t="s">
+      <c r="K83" s="30"/>
+      <c r="L83" s="30"/>
+      <c r="M83" s="30"/>
+      <c r="N83" s="30"/>
+      <c r="O83" s="30"/>
+      <c r="P83" s="30"/>
+      <c r="Q83" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="R83" s="31"/>
-      <c r="S83" s="31"/>
-      <c r="T83" s="31"/>
-      <c r="U83" s="31"/>
-      <c r="V83" s="31"/>
-      <c r="W83" s="31"/>
-      <c r="X83" s="30" t="s">
+      <c r="R83" s="30"/>
+      <c r="S83" s="30"/>
+      <c r="T83" s="30"/>
+      <c r="U83" s="30"/>
+      <c r="V83" s="30"/>
+      <c r="W83" s="30"/>
+      <c r="X83" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="Y83" s="31"/>
-      <c r="Z83" s="31"/>
-      <c r="AA83" s="31"/>
-      <c r="AB83" s="31"/>
-      <c r="AC83" s="31"/>
-      <c r="AD83" s="31"/>
-    </row>
-    <row r="84" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Y83" s="30"/>
+      <c r="Z83" s="30"/>
+      <c r="AA83" s="30"/>
+      <c r="AB83" s="30"/>
+      <c r="AC83" s="30"/>
+      <c r="AD83" s="30"/>
+    </row>
+    <row r="84" spans="2:30" hidden="1">
       <c r="B84" s="1"/>
       <c r="C84" s="2" t="s">
         <v>89</v>
@@ -7561,7 +7614,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:30">
       <c r="B85" s="1" t="s">
         <v>67</v>
       </c>
@@ -7650,7 +7703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:30">
       <c r="B86" s="1" t="s">
         <v>68</v>
       </c>
@@ -7739,7 +7792,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:30">
       <c r="B87" s="1" t="s">
         <v>69</v>
       </c>
@@ -7828,7 +7881,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="88" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:30">
       <c r="B88" s="1" t="s">
         <v>70</v>
       </c>
@@ -7919,17 +7972,35 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="C83:I83"/>
-    <mergeCell ref="J83:P83"/>
-    <mergeCell ref="Q83:W83"/>
-    <mergeCell ref="X83:AD83"/>
-    <mergeCell ref="Q61:W61"/>
-    <mergeCell ref="X61:AD61"/>
-    <mergeCell ref="B68:AD68"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="J76:P76"/>
-    <mergeCell ref="Q76:W76"/>
-    <mergeCell ref="X76:AD76"/>
+    <mergeCell ref="B2:AD2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="J3:P3"/>
+    <mergeCell ref="Q3:W3"/>
+    <mergeCell ref="X3:AD3"/>
+    <mergeCell ref="AF25:AL25"/>
+    <mergeCell ref="AF10:AL10"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:W17"/>
+    <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="AF17:AL17"/>
+    <mergeCell ref="X10:AD10"/>
+    <mergeCell ref="Q10:W10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="J39:P39"/>
+    <mergeCell ref="Q39:W39"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="B24:AD24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:W25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:W32"/>
+    <mergeCell ref="X32:AD32"/>
     <mergeCell ref="AF32:AL32"/>
     <mergeCell ref="C69:I69"/>
     <mergeCell ref="J69:P69"/>
@@ -7946,35 +8017,17 @@
     <mergeCell ref="X54:AD54"/>
     <mergeCell ref="C61:I61"/>
     <mergeCell ref="J61:P61"/>
-    <mergeCell ref="C39:I39"/>
-    <mergeCell ref="J39:P39"/>
-    <mergeCell ref="Q39:W39"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="B24:AD24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:W25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:W32"/>
-    <mergeCell ref="X32:AD32"/>
-    <mergeCell ref="AF25:AL25"/>
-    <mergeCell ref="AF10:AL10"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:W17"/>
-    <mergeCell ref="X17:AD17"/>
-    <mergeCell ref="AF17:AL17"/>
-    <mergeCell ref="X10:AD10"/>
-    <mergeCell ref="Q10:W10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="B2:AD2"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="J3:P3"/>
-    <mergeCell ref="Q3:W3"/>
-    <mergeCell ref="X3:AD3"/>
+    <mergeCell ref="C83:I83"/>
+    <mergeCell ref="J83:P83"/>
+    <mergeCell ref="Q83:W83"/>
+    <mergeCell ref="X83:AD83"/>
+    <mergeCell ref="Q61:W61"/>
+    <mergeCell ref="X61:AD61"/>
+    <mergeCell ref="B68:AD68"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="J76:P76"/>
+    <mergeCell ref="Q76:W76"/>
+    <mergeCell ref="X76:AD76"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -7984,103 +8037,103 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B2:AU113"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="2" style="9" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" style="9" customWidth="1"/>
     <col min="3" max="30" width="7" style="9" customWidth="1"/>
     <col min="31" max="31" width="2" style="9" customWidth="1"/>
-    <col min="32" max="32" width="3.25" style="26" customWidth="1"/>
-    <col min="33" max="16384" width="8.75" style="9"/>
+    <col min="32" max="32" width="3.19921875" style="26" customWidth="1"/>
+    <col min="33" max="16384" width="8.69921875" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:47">
       <c r="B2" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:47">
       <c r="B3" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:47" x14ac:dyDescent="0.25">
-      <c r="B5" s="28" t="s">
+    <row r="5" spans="2:47">
+      <c r="B5" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-    </row>
-    <row r="6" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="32"/>
+    </row>
+    <row r="6" spans="2:47">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="30" t="s">
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="30" t="s">
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="R6" s="31"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="31"/>
-      <c r="X6" s="30" t="s">
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="Y6" s="31"/>
-      <c r="Z6" s="31"/>
-      <c r="AA6" s="31"/>
-      <c r="AB6" s="31"/>
-      <c r="AC6" s="31"/>
-      <c r="AD6" s="31"/>
-    </row>
-    <row r="7" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="30"/>
+    </row>
+    <row r="7" spans="2:47">
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
         <v>75</v>
@@ -8167,7 +8220,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:47">
       <c r="B8" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,7 +8309,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:47">
       <c r="B9" s="1" t="s">
         <v>68</v>
       </c>
@@ -8345,7 +8398,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:47">
       <c r="B10" s="1" t="s">
         <v>69</v>
       </c>
@@ -8434,7 +8487,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:47">
       <c r="B11" s="1" t="s">
         <v>70</v>
       </c>
@@ -8523,7 +8576,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:47">
       <c r="AO12" s="20" t="s">
         <v>96</v>
       </c>
@@ -8531,55 +8584,55 @@
       <c r="AQ12" s="20"/>
       <c r="AR12" s="20"/>
     </row>
-    <row r="13" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:47">
       <c r="B13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="30" t="s">
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="30" t="s">
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="30" t="s">
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31"/>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="31"/>
-      <c r="AC13" s="31"/>
-      <c r="AD13" s="31"/>
-      <c r="AG13" s="30" t="s">
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="30"/>
+      <c r="AA13" s="30"/>
+      <c r="AB13" s="30"/>
+      <c r="AC13" s="30"/>
+      <c r="AD13" s="30"/>
+      <c r="AG13" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="AH13" s="31"/>
-      <c r="AI13" s="31"/>
-      <c r="AJ13" s="31"/>
-      <c r="AK13" s="31"/>
-      <c r="AL13" s="31"/>
-      <c r="AM13" s="31"/>
+      <c r="AH13" s="30"/>
+      <c r="AI13" s="30"/>
+      <c r="AJ13" s="30"/>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="30"/>
+      <c r="AM13" s="30"/>
       <c r="AN13" s="18"/>
       <c r="AO13" s="21" t="s">
         <v>90</v>
@@ -8591,7 +8644,7 @@
       <c r="AT13" s="18"/>
       <c r="AU13" s="18"/>
     </row>
-    <row r="14" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:47">
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
         <v>78</v>
@@ -8721,7 +8774,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:47">
       <c r="B15" s="1" t="s">
         <v>67</v>
       </c>
@@ -8857,7 +8910,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:47">
       <c r="B16" s="1" t="s">
         <v>68</v>
       </c>
@@ -8993,7 +9046,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:47">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -9129,7 +9182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:47">
       <c r="B18" s="1" t="s">
         <v>70</v>
       </c>
@@ -9265,7 +9318,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:47">
       <c r="AG19" s="18"/>
       <c r="AH19" s="18"/>
       <c r="AI19" s="18"/>
@@ -9282,55 +9335,55 @@
       <c r="AT19" s="18"/>
       <c r="AU19" s="18"/>
     </row>
-    <row r="20" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:47">
       <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="30" t="s">
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="30" t="s">
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="30" t="s">
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="Y20" s="31"/>
-      <c r="Z20" s="31"/>
-      <c r="AA20" s="31"/>
-      <c r="AB20" s="31"/>
-      <c r="AC20" s="31"/>
-      <c r="AD20" s="31"/>
-      <c r="AG20" s="30" t="s">
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
+      <c r="AG20" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="AH20" s="31"/>
-      <c r="AI20" s="31"/>
-      <c r="AJ20" s="31"/>
-      <c r="AK20" s="31"/>
-      <c r="AL20" s="31"/>
-      <c r="AM20" s="31"/>
+      <c r="AH20" s="30"/>
+      <c r="AI20" s="30"/>
+      <c r="AJ20" s="30"/>
+      <c r="AK20" s="30"/>
+      <c r="AL20" s="30"/>
+      <c r="AM20" s="30"/>
       <c r="AN20" s="18"/>
       <c r="AO20" s="21" t="s">
         <v>91</v>
@@ -9342,7 +9395,7 @@
       <c r="AT20" s="18"/>
       <c r="AU20" s="18"/>
     </row>
-    <row r="21" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:47">
       <c r="B21" s="1"/>
       <c r="C21" s="2" t="s">
         <v>79</v>
@@ -9472,7 +9525,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:47">
       <c r="B22" s="1" t="s">
         <v>67</v>
       </c>
@@ -9608,7 +9661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:47">
       <c r="B23" s="1" t="s">
         <v>68</v>
       </c>
@@ -9744,7 +9797,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:47">
       <c r="B24" s="1" t="s">
         <v>69</v>
       </c>
@@ -9880,7 +9933,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:47">
       <c r="B25" s="1" t="s">
         <v>70</v>
       </c>
@@ -10016,38 +10069,38 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="2:47" x14ac:dyDescent="0.25">
-      <c r="B27" s="28" t="s">
+    <row r="27" spans="2:47">
+      <c r="B27" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="29"/>
-      <c r="Y27" s="29"/>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="29"/>
-      <c r="AB27" s="29"/>
-      <c r="AC27" s="29"/>
-      <c r="AD27" s="29"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
+      <c r="AA27" s="32"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="32"/>
       <c r="AO27" s="20" t="s">
         <v>95</v>
       </c>
@@ -10055,55 +10108,55 @@
       <c r="AQ27" s="20"/>
       <c r="AR27" s="20"/>
     </row>
-    <row r="28" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:47">
       <c r="B28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="30" t="s">
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="30" t="s">
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="30" t="s">
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-      <c r="AG28" s="30" t="s">
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AG28" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="AH28" s="31"/>
-      <c r="AI28" s="31"/>
-      <c r="AJ28" s="31"/>
-      <c r="AK28" s="31"/>
-      <c r="AL28" s="31"/>
-      <c r="AM28" s="31"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="30"/>
+      <c r="AJ28" s="30"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="30"/>
+      <c r="AM28" s="30"/>
       <c r="AN28" s="18"/>
       <c r="AO28" s="21" t="s">
         <v>90</v>
@@ -10115,7 +10168,7 @@
       <c r="AT28" s="18"/>
       <c r="AU28" s="18"/>
     </row>
-    <row r="29" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:47">
       <c r="B29" s="1"/>
       <c r="C29" s="14" t="s">
         <v>80</v>
@@ -10245,7 +10298,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:47">
       <c r="B30" s="1" t="s">
         <v>67</v>
       </c>
@@ -10379,7 +10432,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:47">
       <c r="B31" s="1" t="s">
         <v>68</v>
       </c>
@@ -10513,7 +10566,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:47">
       <c r="B32" s="1" t="s">
         <v>69</v>
       </c>
@@ -10647,7 +10700,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:47">
       <c r="B33" s="1" t="s">
         <v>70</v>
       </c>
@@ -10781,7 +10834,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:47">
       <c r="AG34" s="18"/>
       <c r="AH34" s="18"/>
       <c r="AI34" s="18"/>
@@ -10798,55 +10851,55 @@
       <c r="AT34" s="18"/>
       <c r="AU34" s="18"/>
     </row>
-    <row r="35" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:47">
       <c r="B35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="30" t="s">
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="30" t="s">
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="30" t="s">
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="Y35" s="31"/>
-      <c r="Z35" s="31"/>
-      <c r="AA35" s="31"/>
-      <c r="AB35" s="31"/>
-      <c r="AC35" s="31"/>
-      <c r="AD35" s="31"/>
-      <c r="AG35" s="30" t="s">
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
+      <c r="AB35" s="30"/>
+      <c r="AC35" s="30"/>
+      <c r="AD35" s="30"/>
+      <c r="AG35" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="AH35" s="31"/>
-      <c r="AI35" s="31"/>
-      <c r="AJ35" s="31"/>
-      <c r="AK35" s="31"/>
-      <c r="AL35" s="31"/>
-      <c r="AM35" s="31"/>
+      <c r="AH35" s="30"/>
+      <c r="AI35" s="30"/>
+      <c r="AJ35" s="30"/>
+      <c r="AK35" s="30"/>
+      <c r="AL35" s="30"/>
+      <c r="AM35" s="30"/>
       <c r="AN35" s="18"/>
       <c r="AO35" s="21" t="s">
         <v>91</v>
@@ -10858,7 +10911,7 @@
       <c r="AT35" s="18"/>
       <c r="AU35" s="18"/>
     </row>
-    <row r="36" spans="2:47" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:47" s="17" customFormat="1">
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="s">
         <v>81</v>
@@ -10988,7 +11041,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:47">
       <c r="B37" s="1" t="s">
         <v>67</v>
       </c>
@@ -11122,7 +11175,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:47">
       <c r="B38" s="1" t="s">
         <v>68</v>
       </c>
@@ -11256,7 +11309,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:47">
       <c r="B39" s="1" t="s">
         <v>69</v>
       </c>
@@ -11390,7 +11443,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:47">
       <c r="B40" s="1" t="s">
         <v>70</v>
       </c>
@@ -11524,48 +11577,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:47">
       <c r="B42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="30" t="s">
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="30" t="s">
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
-      <c r="X42" s="30" t="s">
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="30"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="30"/>
+      <c r="X42" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="Y42" s="31"/>
-      <c r="Z42" s="31"/>
-      <c r="AA42" s="31"/>
-      <c r="AB42" s="31"/>
-      <c r="AC42" s="31"/>
-      <c r="AD42" s="31"/>
-    </row>
-    <row r="43" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="Y42" s="30"/>
+      <c r="Z42" s="30"/>
+      <c r="AA42" s="30"/>
+      <c r="AB42" s="30"/>
+      <c r="AC42" s="30"/>
+      <c r="AD42" s="30"/>
+    </row>
+    <row r="43" spans="2:47">
       <c r="B43" s="1"/>
       <c r="C43" s="14" t="s">
         <v>82</v>
@@ -11652,7 +11705,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:47">
       <c r="B44" s="1" t="s">
         <v>67</v>
       </c>
@@ -11741,7 +11794,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:47">
       <c r="B45" s="1" t="s">
         <v>68</v>
       </c>
@@ -11830,7 +11883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:47">
       <c r="B46" s="1" t="s">
         <v>69</v>
       </c>
@@ -11919,7 +11972,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="2:47" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:47">
       <c r="B47" s="1" t="s">
         <v>70</v>
       </c>
@@ -12008,81 +12061,81 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B49" s="28" t="s">
+    <row r="49" spans="2:30">
+      <c r="B49" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
-      <c r="AA49" s="29"/>
-      <c r="AB49" s="29"/>
-      <c r="AC49" s="29"/>
-      <c r="AD49" s="29"/>
-    </row>
-    <row r="50" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="32"/>
+      <c r="W49" s="32"/>
+      <c r="X49" s="32"/>
+      <c r="Y49" s="32"/>
+      <c r="Z49" s="32"/>
+      <c r="AA49" s="32"/>
+      <c r="AB49" s="32"/>
+      <c r="AC49" s="32"/>
+      <c r="AD49" s="32"/>
+    </row>
+    <row r="50" spans="2:30">
       <c r="B50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="30" t="s">
+      <c r="C50" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="30" t="s">
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-      <c r="N50" s="31"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="31"/>
-      <c r="Q50" s="30" t="s">
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="30"/>
+      <c r="P50" s="30"/>
+      <c r="Q50" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="R50" s="31"/>
-      <c r="S50" s="31"/>
-      <c r="T50" s="31"/>
-      <c r="U50" s="31"/>
-      <c r="V50" s="31"/>
-      <c r="W50" s="31"/>
-      <c r="X50" s="30" t="s">
+      <c r="R50" s="30"/>
+      <c r="S50" s="30"/>
+      <c r="T50" s="30"/>
+      <c r="U50" s="30"/>
+      <c r="V50" s="30"/>
+      <c r="W50" s="30"/>
+      <c r="X50" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="Y50" s="31"/>
-      <c r="Z50" s="31"/>
-      <c r="AA50" s="31"/>
-      <c r="AB50" s="31"/>
-      <c r="AC50" s="31"/>
-      <c r="AD50" s="31"/>
-    </row>
-    <row r="51" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y50" s="30"/>
+      <c r="Z50" s="30"/>
+      <c r="AA50" s="30"/>
+      <c r="AB50" s="30"/>
+      <c r="AC50" s="30"/>
+      <c r="AD50" s="30"/>
+    </row>
+    <row r="51" spans="2:30">
       <c r="B51" s="1"/>
       <c r="C51" s="2" t="s">
         <v>83</v>
@@ -12169,7 +12222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:30">
       <c r="B52" s="1" t="s">
         <v>67</v>
       </c>
@@ -12258,7 +12311,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:30">
       <c r="B53" s="1" t="s">
         <v>68</v>
       </c>
@@ -12347,7 +12400,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:30">
       <c r="B54" s="1" t="s">
         <v>69</v>
       </c>
@@ -12436,7 +12489,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:30">
       <c r="B55" s="1" t="s">
         <v>70</v>
       </c>
@@ -12525,48 +12578,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:30">
       <c r="B57" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="30" t="s">
+      <c r="C57" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D57" s="31"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="31"/>
-      <c r="I57" s="31"/>
-      <c r="J57" s="30" t="s">
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="31"/>
-      <c r="N57" s="31"/>
-      <c r="O57" s="31"/>
-      <c r="P57" s="31"/>
-      <c r="Q57" s="30" t="s">
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="30"/>
+      <c r="O57" s="30"/>
+      <c r="P57" s="30"/>
+      <c r="Q57" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="R57" s="31"/>
-      <c r="S57" s="31"/>
-      <c r="T57" s="31"/>
-      <c r="U57" s="31"/>
-      <c r="V57" s="31"/>
-      <c r="W57" s="31"/>
-      <c r="X57" s="30" t="s">
+      <c r="R57" s="30"/>
+      <c r="S57" s="30"/>
+      <c r="T57" s="30"/>
+      <c r="U57" s="30"/>
+      <c r="V57" s="30"/>
+      <c r="W57" s="30"/>
+      <c r="X57" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="Y57" s="31"/>
-      <c r="Z57" s="31"/>
-      <c r="AA57" s="31"/>
-      <c r="AB57" s="31"/>
-      <c r="AC57" s="31"/>
-      <c r="AD57" s="31"/>
-    </row>
-    <row r="58" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y57" s="30"/>
+      <c r="Z57" s="30"/>
+      <c r="AA57" s="30"/>
+      <c r="AB57" s="30"/>
+      <c r="AC57" s="30"/>
+      <c r="AD57" s="30"/>
+    </row>
+    <row r="58" spans="2:30">
       <c r="B58" s="1"/>
       <c r="C58" s="2" t="s">
         <v>84</v>
@@ -12653,7 +12706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:30">
       <c r="B59" s="1" t="s">
         <v>67</v>
       </c>
@@ -12742,7 +12795,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:30">
       <c r="B60" s="1" t="s">
         <v>68</v>
       </c>
@@ -12831,7 +12884,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:30">
       <c r="B61" s="1" t="s">
         <v>69</v>
       </c>
@@ -12920,7 +12973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:30">
       <c r="B62" s="1" t="s">
         <v>70</v>
       </c>
@@ -13009,48 +13062,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:30">
       <c r="B64" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="30" t="s">
+      <c r="C64" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="30" t="s">
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
-      <c r="N64" s="31"/>
-      <c r="O64" s="31"/>
-      <c r="P64" s="31"/>
-      <c r="Q64" s="30" t="s">
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="R64" s="31"/>
-      <c r="S64" s="31"/>
-      <c r="T64" s="31"/>
-      <c r="U64" s="31"/>
-      <c r="V64" s="31"/>
-      <c r="W64" s="31"/>
-      <c r="X64" s="30" t="s">
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="Y64" s="31"/>
-      <c r="Z64" s="31"/>
-      <c r="AA64" s="31"/>
-      <c r="AB64" s="31"/>
-      <c r="AC64" s="31"/>
-      <c r="AD64" s="31"/>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="30"/>
+      <c r="AB64" s="30"/>
+      <c r="AC64" s="30"/>
+      <c r="AD64" s="30"/>
+    </row>
+    <row r="65" spans="2:30">
       <c r="B65" s="1"/>
       <c r="C65" s="2" t="s">
         <v>86</v>
@@ -13137,7 +13190,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:30">
       <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
@@ -13226,7 +13279,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:30">
       <c r="B67" s="1" t="s">
         <v>68</v>
       </c>
@@ -13315,7 +13368,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:30">
       <c r="B68" s="1" t="s">
         <v>69</v>
       </c>
@@ -13404,7 +13457,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:30">
       <c r="B69" s="1" t="s">
         <v>70</v>
       </c>
@@ -13493,81 +13546,81 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B71" s="28" t="s">
+    <row r="71" spans="2:30">
+      <c r="B71" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="29"/>
-      <c r="I71" s="29"/>
-      <c r="J71" s="29"/>
-      <c r="K71" s="29"/>
-      <c r="L71" s="29"/>
-      <c r="M71" s="29"/>
-      <c r="N71" s="29"/>
-      <c r="O71" s="29"/>
-      <c r="P71" s="29"/>
-      <c r="Q71" s="29"/>
-      <c r="R71" s="29"/>
-      <c r="S71" s="29"/>
-      <c r="T71" s="29"/>
-      <c r="U71" s="29"/>
-      <c r="V71" s="29"/>
-      <c r="W71" s="29"/>
-      <c r="X71" s="29"/>
-      <c r="Y71" s="29"/>
-      <c r="Z71" s="29"/>
-      <c r="AA71" s="29"/>
-      <c r="AB71" s="29"/>
-      <c r="AC71" s="29"/>
-      <c r="AD71" s="29"/>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
+      <c r="L71" s="32"/>
+      <c r="M71" s="32"/>
+      <c r="N71" s="32"/>
+      <c r="O71" s="32"/>
+      <c r="P71" s="32"/>
+      <c r="Q71" s="32"/>
+      <c r="R71" s="32"/>
+      <c r="S71" s="32"/>
+      <c r="T71" s="32"/>
+      <c r="U71" s="32"/>
+      <c r="V71" s="32"/>
+      <c r="W71" s="32"/>
+      <c r="X71" s="32"/>
+      <c r="Y71" s="32"/>
+      <c r="Z71" s="32"/>
+      <c r="AA71" s="32"/>
+      <c r="AB71" s="32"/>
+      <c r="AC71" s="32"/>
+      <c r="AD71" s="32"/>
+    </row>
+    <row r="72" spans="2:30">
       <c r="B72" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C72" s="30" t="s">
+      <c r="C72" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="30" t="s">
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="30"/>
+      <c r="J72" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="K72" s="31"/>
-      <c r="L72" s="31"/>
-      <c r="M72" s="31"/>
-      <c r="N72" s="31"/>
-      <c r="O72" s="31"/>
-      <c r="P72" s="31"/>
-      <c r="Q72" s="30" t="s">
+      <c r="K72" s="30"/>
+      <c r="L72" s="30"/>
+      <c r="M72" s="30"/>
+      <c r="N72" s="30"/>
+      <c r="O72" s="30"/>
+      <c r="P72" s="30"/>
+      <c r="Q72" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R72" s="31"/>
-      <c r="S72" s="31"/>
-      <c r="T72" s="31"/>
-      <c r="U72" s="31"/>
-      <c r="V72" s="31"/>
-      <c r="W72" s="31"/>
-      <c r="X72" s="30" t="s">
+      <c r="R72" s="30"/>
+      <c r="S72" s="30"/>
+      <c r="T72" s="30"/>
+      <c r="U72" s="30"/>
+      <c r="V72" s="30"/>
+      <c r="W72" s="30"/>
+      <c r="X72" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="Y72" s="31"/>
-      <c r="Z72" s="31"/>
-      <c r="AA72" s="31"/>
-      <c r="AB72" s="31"/>
-      <c r="AC72" s="31"/>
-      <c r="AD72" s="31"/>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y72" s="30"/>
+      <c r="Z72" s="30"/>
+      <c r="AA72" s="30"/>
+      <c r="AB72" s="30"/>
+      <c r="AC72" s="30"/>
+      <c r="AD72" s="30"/>
+    </row>
+    <row r="73" spans="2:30">
       <c r="B73" s="1"/>
       <c r="C73" s="2" t="s">
         <v>87</v>
@@ -13654,7 +13707,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:30">
       <c r="B74" s="1" t="s">
         <v>67</v>
       </c>
@@ -13743,7 +13796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:30">
       <c r="B75" s="1" t="s">
         <v>68</v>
       </c>
@@ -13832,7 +13885,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:30">
       <c r="B76" s="1" t="s">
         <v>69</v>
       </c>
@@ -13921,7 +13974,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:30">
       <c r="B77" s="1" t="s">
         <v>70</v>
       </c>
@@ -14010,48 +14063,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:30">
       <c r="B79" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C79" s="30" t="s">
+      <c r="C79" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
-      <c r="J79" s="30" t="s">
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
+      <c r="J79" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="K79" s="31"/>
-      <c r="L79" s="31"/>
-      <c r="M79" s="31"/>
-      <c r="N79" s="31"/>
-      <c r="O79" s="31"/>
-      <c r="P79" s="31"/>
-      <c r="Q79" s="30" t="s">
+      <c r="K79" s="30"/>
+      <c r="L79" s="30"/>
+      <c r="M79" s="30"/>
+      <c r="N79" s="30"/>
+      <c r="O79" s="30"/>
+      <c r="P79" s="30"/>
+      <c r="Q79" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="R79" s="31"/>
-      <c r="S79" s="31"/>
-      <c r="T79" s="31"/>
-      <c r="U79" s="31"/>
-      <c r="V79" s="31"/>
-      <c r="W79" s="31"/>
-      <c r="X79" s="30" t="s">
+      <c r="R79" s="30"/>
+      <c r="S79" s="30"/>
+      <c r="T79" s="30"/>
+      <c r="U79" s="30"/>
+      <c r="V79" s="30"/>
+      <c r="W79" s="30"/>
+      <c r="X79" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="Y79" s="31"/>
-      <c r="Z79" s="31"/>
-      <c r="AA79" s="31"/>
-      <c r="AB79" s="31"/>
-      <c r="AC79" s="31"/>
-      <c r="AD79" s="31"/>
-    </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y79" s="30"/>
+      <c r="Z79" s="30"/>
+      <c r="AA79" s="30"/>
+      <c r="AB79" s="30"/>
+      <c r="AC79" s="30"/>
+      <c r="AD79" s="30"/>
+    </row>
+    <row r="80" spans="2:30">
       <c r="B80" s="1"/>
       <c r="C80" s="2" t="s">
         <v>88</v>
@@ -14138,7 +14191,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:30">
       <c r="B81" s="1" t="s">
         <v>67</v>
       </c>
@@ -14227,7 +14280,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:30">
       <c r="B82" s="1" t="s">
         <v>68</v>
       </c>
@@ -14316,7 +14369,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:30">
       <c r="B83" s="1" t="s">
         <v>69</v>
       </c>
@@ -14405,7 +14458,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:30">
       <c r="B84" s="1" t="s">
         <v>70</v>
       </c>
@@ -14494,48 +14547,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:30">
       <c r="B86" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C86" s="30" t="s">
+      <c r="C86" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D86" s="31"/>
-      <c r="E86" s="31"/>
-      <c r="F86" s="31"/>
-      <c r="G86" s="31"/>
-      <c r="H86" s="31"/>
-      <c r="I86" s="31"/>
-      <c r="J86" s="30" t="s">
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
+      <c r="J86" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="K86" s="31"/>
-      <c r="L86" s="31"/>
-      <c r="M86" s="31"/>
-      <c r="N86" s="31"/>
-      <c r="O86" s="31"/>
-      <c r="P86" s="31"/>
-      <c r="Q86" s="30" t="s">
+      <c r="K86" s="30"/>
+      <c r="L86" s="30"/>
+      <c r="M86" s="30"/>
+      <c r="N86" s="30"/>
+      <c r="O86" s="30"/>
+      <c r="P86" s="30"/>
+      <c r="Q86" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="R86" s="31"/>
-      <c r="S86" s="31"/>
-      <c r="T86" s="31"/>
-      <c r="U86" s="31"/>
-      <c r="V86" s="31"/>
-      <c r="W86" s="31"/>
-      <c r="X86" s="30" t="s">
+      <c r="R86" s="30"/>
+      <c r="S86" s="30"/>
+      <c r="T86" s="30"/>
+      <c r="U86" s="30"/>
+      <c r="V86" s="30"/>
+      <c r="W86" s="30"/>
+      <c r="X86" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="Y86" s="31"/>
-      <c r="Z86" s="31"/>
-      <c r="AA86" s="31"/>
-      <c r="AB86" s="31"/>
-      <c r="AC86" s="31"/>
-      <c r="AD86" s="31"/>
-    </row>
-    <row r="87" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y86" s="30"/>
+      <c r="Z86" s="30"/>
+      <c r="AA86" s="30"/>
+      <c r="AB86" s="30"/>
+      <c r="AC86" s="30"/>
+      <c r="AD86" s="30"/>
+    </row>
+    <row r="87" spans="2:30">
       <c r="B87" s="1"/>
       <c r="C87" s="2" t="s">
         <v>89</v>
@@ -14622,7 +14675,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:30">
       <c r="B88" s="1" t="s">
         <v>67</v>
       </c>
@@ -14711,7 +14764,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:30">
       <c r="B89" s="1" t="s">
         <v>68</v>
       </c>
@@ -14800,7 +14853,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:30">
       <c r="B90" s="1" t="s">
         <v>69</v>
       </c>
@@ -14889,7 +14942,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="91" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:30">
       <c r="B91" s="1" t="s">
         <v>70</v>
       </c>
@@ -14978,81 +15031,81 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B93" s="28" t="s">
+    <row r="93" spans="2:30">
+      <c r="B93" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="C93" s="29"/>
-      <c r="D93" s="29"/>
-      <c r="E93" s="29"/>
-      <c r="F93" s="29"/>
-      <c r="G93" s="29"/>
-      <c r="H93" s="29"/>
-      <c r="I93" s="29"/>
-      <c r="J93" s="29"/>
-      <c r="K93" s="29"/>
-      <c r="L93" s="29"/>
-      <c r="M93" s="29"/>
-      <c r="N93" s="29"/>
-      <c r="O93" s="29"/>
-      <c r="P93" s="29"/>
-      <c r="Q93" s="29"/>
-      <c r="R93" s="29"/>
-      <c r="S93" s="29"/>
-      <c r="T93" s="29"/>
-      <c r="U93" s="29"/>
-      <c r="V93" s="29"/>
-      <c r="W93" s="29"/>
-      <c r="X93" s="29"/>
-      <c r="Y93" s="29"/>
-      <c r="Z93" s="29"/>
-      <c r="AA93" s="29"/>
-      <c r="AB93" s="29"/>
-      <c r="AC93" s="29"/>
-      <c r="AD93" s="29"/>
-    </row>
-    <row r="94" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="C93" s="32"/>
+      <c r="D93" s="32"/>
+      <c r="E93" s="32"/>
+      <c r="F93" s="32"/>
+      <c r="G93" s="32"/>
+      <c r="H93" s="32"/>
+      <c r="I93" s="32"/>
+      <c r="J93" s="32"/>
+      <c r="K93" s="32"/>
+      <c r="L93" s="32"/>
+      <c r="M93" s="32"/>
+      <c r="N93" s="32"/>
+      <c r="O93" s="32"/>
+      <c r="P93" s="32"/>
+      <c r="Q93" s="32"/>
+      <c r="R93" s="32"/>
+      <c r="S93" s="32"/>
+      <c r="T93" s="32"/>
+      <c r="U93" s="32"/>
+      <c r="V93" s="32"/>
+      <c r="W93" s="32"/>
+      <c r="X93" s="32"/>
+      <c r="Y93" s="32"/>
+      <c r="Z93" s="32"/>
+      <c r="AA93" s="32"/>
+      <c r="AB93" s="32"/>
+      <c r="AC93" s="32"/>
+      <c r="AD93" s="32"/>
+    </row>
+    <row r="94" spans="2:30">
       <c r="B94" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C94" s="30" t="s">
+      <c r="C94" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D94" s="31"/>
-      <c r="E94" s="31"/>
-      <c r="F94" s="31"/>
-      <c r="G94" s="31"/>
-      <c r="H94" s="31"/>
-      <c r="I94" s="31"/>
-      <c r="J94" s="30" t="s">
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="30"/>
+      <c r="G94" s="30"/>
+      <c r="H94" s="30"/>
+      <c r="I94" s="30"/>
+      <c r="J94" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="K94" s="31"/>
-      <c r="L94" s="31"/>
-      <c r="M94" s="31"/>
-      <c r="N94" s="31"/>
-      <c r="O94" s="31"/>
-      <c r="P94" s="31"/>
-      <c r="Q94" s="30" t="s">
+      <c r="K94" s="30"/>
+      <c r="L94" s="30"/>
+      <c r="M94" s="30"/>
+      <c r="N94" s="30"/>
+      <c r="O94" s="30"/>
+      <c r="P94" s="30"/>
+      <c r="Q94" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="R94" s="31"/>
-      <c r="S94" s="31"/>
-      <c r="T94" s="31"/>
-      <c r="U94" s="31"/>
-      <c r="V94" s="31"/>
-      <c r="W94" s="31"/>
-      <c r="X94" s="30" t="s">
+      <c r="R94" s="30"/>
+      <c r="S94" s="30"/>
+      <c r="T94" s="30"/>
+      <c r="U94" s="30"/>
+      <c r="V94" s="30"/>
+      <c r="W94" s="30"/>
+      <c r="X94" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="Y94" s="31"/>
-      <c r="Z94" s="31"/>
-      <c r="AA94" s="31"/>
-      <c r="AB94" s="31"/>
-      <c r="AC94" s="31"/>
-      <c r="AD94" s="31"/>
-    </row>
-    <row r="95" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y94" s="30"/>
+      <c r="Z94" s="30"/>
+      <c r="AA94" s="30"/>
+      <c r="AB94" s="30"/>
+      <c r="AC94" s="30"/>
+      <c r="AD94" s="30"/>
+    </row>
+    <row r="95" spans="2:30">
       <c r="B95" s="1"/>
       <c r="C95" s="2" t="s">
         <v>99</v>
@@ -15139,7 +15192,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:30">
       <c r="B96" s="1" t="s">
         <v>67</v>
       </c>
@@ -15228,7 +15281,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:30">
       <c r="B97" s="1" t="s">
         <v>68</v>
       </c>
@@ -15317,7 +15370,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:30">
       <c r="B98" s="1" t="s">
         <v>69</v>
       </c>
@@ -15406,7 +15459,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="99" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:30">
       <c r="B99" s="1" t="s">
         <v>70</v>
       </c>
@@ -15495,7 +15548,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="100" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:30">
       <c r="B100" s="27"/>
       <c r="C100" s="27"/>
       <c r="D100" s="27"/>
@@ -15526,48 +15579,48 @@
       <c r="AC100" s="27"/>
       <c r="AD100" s="27"/>
     </row>
-    <row r="101" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:30">
       <c r="B101" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C101" s="30" t="s">
+      <c r="C101" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D101" s="31"/>
-      <c r="E101" s="31"/>
-      <c r="F101" s="31"/>
-      <c r="G101" s="31"/>
-      <c r="H101" s="31"/>
-      <c r="I101" s="31"/>
-      <c r="J101" s="30" t="s">
+      <c r="D101" s="30"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
+      <c r="H101" s="30"/>
+      <c r="I101" s="30"/>
+      <c r="J101" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="K101" s="31"/>
-      <c r="L101" s="31"/>
-      <c r="M101" s="31"/>
-      <c r="N101" s="31"/>
-      <c r="O101" s="31"/>
-      <c r="P101" s="31"/>
-      <c r="Q101" s="30" t="s">
+      <c r="K101" s="30"/>
+      <c r="L101" s="30"/>
+      <c r="M101" s="30"/>
+      <c r="N101" s="30"/>
+      <c r="O101" s="30"/>
+      <c r="P101" s="30"/>
+      <c r="Q101" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="R101" s="31"/>
-      <c r="S101" s="31"/>
-      <c r="T101" s="31"/>
-      <c r="U101" s="31"/>
-      <c r="V101" s="31"/>
-      <c r="W101" s="31"/>
-      <c r="X101" s="30" t="s">
+      <c r="R101" s="30"/>
+      <c r="S101" s="30"/>
+      <c r="T101" s="30"/>
+      <c r="U101" s="30"/>
+      <c r="V101" s="30"/>
+      <c r="W101" s="30"/>
+      <c r="X101" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="Y101" s="31"/>
-      <c r="Z101" s="31"/>
-      <c r="AA101" s="31"/>
-      <c r="AB101" s="31"/>
-      <c r="AC101" s="31"/>
-      <c r="AD101" s="31"/>
-    </row>
-    <row r="102" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y101" s="30"/>
+      <c r="Z101" s="30"/>
+      <c r="AA101" s="30"/>
+      <c r="AB101" s="30"/>
+      <c r="AC101" s="30"/>
+      <c r="AD101" s="30"/>
+    </row>
+    <row r="102" spans="2:30">
       <c r="B102" s="1"/>
       <c r="C102" s="2" t="s">
         <v>99</v>
@@ -15654,7 +15707,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:30">
       <c r="B103" s="1" t="s">
         <v>67</v>
       </c>
@@ -15743,7 +15796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:30">
       <c r="B104" s="1" t="s">
         <v>68</v>
       </c>
@@ -15832,7 +15885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:30">
       <c r="B105" s="1" t="s">
         <v>69</v>
       </c>
@@ -15921,7 +15974,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="106" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:30">
       <c r="B106" s="1" t="s">
         <v>70</v>
       </c>
@@ -16010,7 +16063,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="107" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:30">
       <c r="B107" s="27"/>
       <c r="C107" s="27"/>
       <c r="D107" s="27"/>
@@ -16041,48 +16094,48 @@
       <c r="AC107" s="27"/>
       <c r="AD107" s="27"/>
     </row>
-    <row r="108" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:30">
       <c r="B108" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C108" s="30" t="s">
+      <c r="C108" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D108" s="31"/>
-      <c r="E108" s="31"/>
-      <c r="F108" s="31"/>
-      <c r="G108" s="31"/>
-      <c r="H108" s="31"/>
-      <c r="I108" s="31"/>
-      <c r="J108" s="30" t="s">
+      <c r="D108" s="30"/>
+      <c r="E108" s="30"/>
+      <c r="F108" s="30"/>
+      <c r="G108" s="30"/>
+      <c r="H108" s="30"/>
+      <c r="I108" s="30"/>
+      <c r="J108" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="K108" s="31"/>
-      <c r="L108" s="31"/>
-      <c r="M108" s="31"/>
-      <c r="N108" s="31"/>
-      <c r="O108" s="31"/>
-      <c r="P108" s="31"/>
-      <c r="Q108" s="30" t="s">
+      <c r="K108" s="30"/>
+      <c r="L108" s="30"/>
+      <c r="M108" s="30"/>
+      <c r="N108" s="30"/>
+      <c r="O108" s="30"/>
+      <c r="P108" s="30"/>
+      <c r="Q108" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="R108" s="31"/>
-      <c r="S108" s="31"/>
-      <c r="T108" s="31"/>
-      <c r="U108" s="31"/>
-      <c r="V108" s="31"/>
-      <c r="W108" s="31"/>
-      <c r="X108" s="30" t="s">
+      <c r="R108" s="30"/>
+      <c r="S108" s="30"/>
+      <c r="T108" s="30"/>
+      <c r="U108" s="30"/>
+      <c r="V108" s="30"/>
+      <c r="W108" s="30"/>
+      <c r="X108" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="Y108" s="31"/>
-      <c r="Z108" s="31"/>
-      <c r="AA108" s="31"/>
-      <c r="AB108" s="31"/>
-      <c r="AC108" s="31"/>
-      <c r="AD108" s="31"/>
-    </row>
-    <row r="109" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y108" s="30"/>
+      <c r="Z108" s="30"/>
+      <c r="AA108" s="30"/>
+      <c r="AB108" s="30"/>
+      <c r="AC108" s="30"/>
+      <c r="AD108" s="30"/>
+    </row>
+    <row r="109" spans="2:30">
       <c r="B109" s="1"/>
       <c r="C109" s="2" t="s">
         <v>93</v>
@@ -16169,7 +16222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:30">
       <c r="B110" s="1" t="s">
         <v>67</v>
       </c>
@@ -16258,7 +16311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:30">
       <c r="B111" s="1" t="s">
         <v>68</v>
       </c>
@@ -16347,7 +16400,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:30">
       <c r="B112" s="1" t="s">
         <v>69</v>
       </c>
@@ -16436,7 +16489,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="113" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:30">
       <c r="B113" s="1" t="s">
         <v>70</v>
       </c>
@@ -16527,23 +16580,42 @@
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="C101:I101"/>
-    <mergeCell ref="J101:P101"/>
-    <mergeCell ref="Q101:W101"/>
-    <mergeCell ref="X101:AD101"/>
-    <mergeCell ref="C108:I108"/>
-    <mergeCell ref="J108:P108"/>
-    <mergeCell ref="Q108:W108"/>
-    <mergeCell ref="X108:AD108"/>
-    <mergeCell ref="C86:I86"/>
-    <mergeCell ref="Q86:W86"/>
-    <mergeCell ref="J86:P86"/>
-    <mergeCell ref="B93:AD93"/>
-    <mergeCell ref="C94:I94"/>
-    <mergeCell ref="J94:P94"/>
-    <mergeCell ref="Q94:W94"/>
-    <mergeCell ref="X94:AD94"/>
-    <mergeCell ref="X86:AD86"/>
+    <mergeCell ref="AG28:AM28"/>
+    <mergeCell ref="AG35:AM35"/>
+    <mergeCell ref="AG20:AM20"/>
+    <mergeCell ref="AG13:AM13"/>
+    <mergeCell ref="X13:AD13"/>
+    <mergeCell ref="J6:P6"/>
+    <mergeCell ref="X64:AD64"/>
+    <mergeCell ref="X42:AD42"/>
+    <mergeCell ref="J50:P50"/>
+    <mergeCell ref="X6:AD6"/>
+    <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="B49:AD49"/>
+    <mergeCell ref="Q6:W6"/>
+    <mergeCell ref="X28:AD28"/>
+    <mergeCell ref="Q28:W28"/>
+    <mergeCell ref="Q20:W20"/>
+    <mergeCell ref="B27:AD27"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="Q35:W35"/>
+    <mergeCell ref="C50:I50"/>
+    <mergeCell ref="C79:I79"/>
+    <mergeCell ref="J42:P42"/>
+    <mergeCell ref="C64:I64"/>
+    <mergeCell ref="Q64:W64"/>
+    <mergeCell ref="Q57:W57"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="B71:AD71"/>
+    <mergeCell ref="C42:I42"/>
+    <mergeCell ref="Q42:W42"/>
+    <mergeCell ref="J79:P79"/>
+    <mergeCell ref="J57:P57"/>
+    <mergeCell ref="Q50:W50"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="J72:P72"/>
     <mergeCell ref="X50:AD50"/>
     <mergeCell ref="X79:AD79"/>
     <mergeCell ref="Q79:W79"/>
@@ -16560,42 +16632,2664 @@
     <mergeCell ref="C35:I35"/>
     <mergeCell ref="C72:I72"/>
     <mergeCell ref="J35:P35"/>
-    <mergeCell ref="J57:P57"/>
-    <mergeCell ref="Q50:W50"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="J72:P72"/>
-    <mergeCell ref="C79:I79"/>
-    <mergeCell ref="J42:P42"/>
-    <mergeCell ref="C64:I64"/>
-    <mergeCell ref="Q64:W64"/>
-    <mergeCell ref="Q57:W57"/>
-    <mergeCell ref="C57:I57"/>
-    <mergeCell ref="B71:AD71"/>
-    <mergeCell ref="C42:I42"/>
-    <mergeCell ref="Q42:W42"/>
-    <mergeCell ref="J79:P79"/>
+    <mergeCell ref="C86:I86"/>
+    <mergeCell ref="Q86:W86"/>
+    <mergeCell ref="J86:P86"/>
+    <mergeCell ref="B93:AD93"/>
+    <mergeCell ref="C94:I94"/>
+    <mergeCell ref="J94:P94"/>
+    <mergeCell ref="Q94:W94"/>
+    <mergeCell ref="X94:AD94"/>
+    <mergeCell ref="X86:AD86"/>
+    <mergeCell ref="C101:I101"/>
+    <mergeCell ref="J101:P101"/>
+    <mergeCell ref="Q101:W101"/>
+    <mergeCell ref="X101:AD101"/>
+    <mergeCell ref="C108:I108"/>
+    <mergeCell ref="J108:P108"/>
+    <mergeCell ref="Q108:W108"/>
+    <mergeCell ref="X108:AD108"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B2:AD43"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="2" style="28" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" style="28" customWidth="1"/>
+    <col min="3" max="30" width="7" style="28" customWidth="1"/>
+    <col min="31" max="16384" width="8.69921875" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:30">
+      <c r="B2" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="2:30">
+      <c r="B3" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:30">
+      <c r="B5" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="32"/>
+    </row>
+    <row r="6" spans="2:30">
+      <c r="B6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="R6" s="37"/>
+      <c r="S6" s="37"/>
+      <c r="T6" s="37"/>
+      <c r="U6" s="37"/>
+      <c r="V6" s="37"/>
+      <c r="W6" s="37"/>
+      <c r="X6" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y6" s="37"/>
+      <c r="Z6" s="37"/>
+      <c r="AA6" s="37"/>
+      <c r="AB6" s="37"/>
+      <c r="AC6" s="37"/>
+      <c r="AD6" s="37"/>
+    </row>
+    <row r="7" spans="2:30">
+      <c r="B7" s="1"/>
+      <c r="C7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD7" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:30">
+      <c r="B8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:30">
+      <c r="B9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:30">
+      <c r="B10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD10" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="2:30">
+      <c r="B11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W11" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD11" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30">
+      <c r="B13" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="32"/>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="32"/>
+    </row>
+    <row r="14" spans="2:30">
+      <c r="B14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="R14" s="37"/>
+      <c r="S14" s="37"/>
+      <c r="T14" s="37"/>
+      <c r="U14" s="37"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y14" s="37"/>
+      <c r="Z14" s="37"/>
+      <c r="AA14" s="37"/>
+      <c r="AB14" s="37"/>
+      <c r="AC14" s="37"/>
+      <c r="AD14" s="37"/>
+    </row>
+    <row r="15" spans="2:30">
+      <c r="B15" s="1"/>
+      <c r="C15" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD15" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:30">
+      <c r="B16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W16" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD16" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:30">
+      <c r="B17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD17" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:30">
+      <c r="B18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD18" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:30">
+      <c r="B19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P19" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD19" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:30">
+      <c r="B21" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="32"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+    </row>
+    <row r="22" spans="2:30">
+      <c r="B22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="R22" s="37"/>
+      <c r="S22" s="37"/>
+      <c r="T22" s="37"/>
+      <c r="U22" s="37"/>
+      <c r="V22" s="37"/>
+      <c r="W22" s="37"/>
+      <c r="X22" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y22" s="37"/>
+      <c r="Z22" s="37"/>
+      <c r="AA22" s="37"/>
+      <c r="AB22" s="37"/>
+      <c r="AC22" s="37"/>
+      <c r="AD22" s="37"/>
+    </row>
+    <row r="23" spans="2:30">
+      <c r="B23" s="1"/>
+      <c r="C23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD23" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="2:30">
+      <c r="B24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P24" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W24" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD24" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="2:30">
+      <c r="B25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W25" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD25" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="2:30">
+      <c r="B26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD26" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="2:30">
+      <c r="B27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD27" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="2:30">
+      <c r="B29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="32"/>
+      <c r="X29" s="32"/>
+      <c r="Y29" s="32"/>
+      <c r="Z29" s="32"/>
+      <c r="AA29" s="32"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
+    </row>
+    <row r="30" spans="2:30">
+      <c r="B30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="R30" s="37"/>
+      <c r="S30" s="37"/>
+      <c r="T30" s="37"/>
+      <c r="U30" s="37"/>
+      <c r="V30" s="37"/>
+      <c r="W30" s="37"/>
+      <c r="X30" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y30" s="37"/>
+      <c r="Z30" s="37"/>
+      <c r="AA30" s="37"/>
+      <c r="AB30" s="37"/>
+      <c r="AC30" s="37"/>
+      <c r="AD30" s="37"/>
+    </row>
+    <row r="31" spans="2:30">
+      <c r="B31" s="1"/>
+      <c r="C31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD31" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="2:30">
+      <c r="B32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD32" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30">
+      <c r="B33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P33" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W33" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD33" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30">
+      <c r="B34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P34" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W34" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD34" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30">
+      <c r="B35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD35" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30">
+      <c r="B37" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
+      <c r="V37" s="32"/>
+      <c r="W37" s="32"/>
+      <c r="X37" s="32"/>
+      <c r="Y37" s="32"/>
+      <c r="Z37" s="32"/>
+      <c r="AA37" s="32"/>
+      <c r="AB37" s="32"/>
+      <c r="AC37" s="32"/>
+      <c r="AD37" s="32"/>
+    </row>
+    <row r="38" spans="2:30">
+      <c r="B38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="R38" s="37"/>
+      <c r="S38" s="37"/>
+      <c r="T38" s="37"/>
+      <c r="U38" s="37"/>
+      <c r="V38" s="37"/>
+      <c r="W38" s="37"/>
+      <c r="X38" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y38" s="37"/>
+      <c r="Z38" s="37"/>
+      <c r="AA38" s="37"/>
+      <c r="AB38" s="37"/>
+      <c r="AC38" s="37"/>
+      <c r="AD38" s="37"/>
+    </row>
+    <row r="39" spans="2:30">
+      <c r="B39" s="1"/>
+      <c r="C39" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W39" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD39" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:30">
+      <c r="B40" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD40" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="2:30">
+      <c r="B41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD41" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30">
+      <c r="B42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P42" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W42" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD42" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30">
+      <c r="B43" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P43" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W43" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD43" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="B37:AD37"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="J38:P38"/>
+    <mergeCell ref="Q38:W38"/>
+    <mergeCell ref="X38:AD38"/>
+    <mergeCell ref="B29:AD29"/>
+    <mergeCell ref="C30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="X30:AD30"/>
+    <mergeCell ref="B21:AD21"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:W22"/>
+    <mergeCell ref="X22:AD22"/>
+    <mergeCell ref="B13:AD13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:W14"/>
+    <mergeCell ref="X14:AD14"/>
+    <mergeCell ref="B5:AD5"/>
+    <mergeCell ref="C6:I6"/>
     <mergeCell ref="J6:P6"/>
-    <mergeCell ref="X64:AD64"/>
-    <mergeCell ref="X42:AD42"/>
-    <mergeCell ref="J50:P50"/>
+    <mergeCell ref="Q6:W6"/>
     <mergeCell ref="X6:AD6"/>
-    <mergeCell ref="X20:AD20"/>
-    <mergeCell ref="B49:AD49"/>
-    <mergeCell ref="Q6:W6"/>
-    <mergeCell ref="X28:AD28"/>
-    <mergeCell ref="Q28:W28"/>
-    <mergeCell ref="Q20:W20"/>
-    <mergeCell ref="B27:AD27"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="Q35:W35"/>
-    <mergeCell ref="C50:I50"/>
-    <mergeCell ref="AG28:AM28"/>
-    <mergeCell ref="AG35:AM35"/>
-    <mergeCell ref="AG20:AM20"/>
-    <mergeCell ref="AG13:AM13"/>
-    <mergeCell ref="X13:AD13"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
